--- a/AAII_Financials/Quarterly/GRFS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/GRFS_QTR_FIN.xlsx
@@ -656,355 +656,368 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AB102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45657</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44377</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44286</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44196</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44104</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44012</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43921</v>
       </c>
-      <c r="Z7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AA7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>2141000</v>
+      </c>
+      <c r="E8" s="3">
         <v>2326700</v>
       </c>
-      <c r="E8" s="3">
-        <v>2220900</v>
-      </c>
       <c r="F8" s="3">
+        <v>2221000</v>
+      </c>
+      <c r="G8" s="3">
         <v>2045200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1947800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1956000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1816000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1830400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1612900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1690800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1816000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1696500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1897300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1665400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1678800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1374900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>5348000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1455900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1253400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1385200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1381600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1436500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1342300</v>
       </c>
-      <c r="Z8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>1358400</v>
+      </c>
+      <c r="E9" s="3">
         <v>1504200</v>
       </c>
-      <c r="E9" s="3">
-        <v>1347400</v>
-      </c>
       <c r="F9" s="3">
+        <v>1358600</v>
+      </c>
+      <c r="G9" s="3">
         <v>1241700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1229500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1132500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1150900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1190700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1008700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1022100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1150900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1094100</v>
       </c>
-      <c r="O9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="Q9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R9" s="3">
         <v>1050000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>838300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>3220300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>830400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>689200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>760500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>742500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>972100</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>728700</v>
       </c>
-      <c r="Z9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>782600</v>
+      </c>
+      <c r="E10" s="3">
         <v>822500</v>
       </c>
-      <c r="E10" s="3">
-        <v>873500</v>
-      </c>
       <c r="F10" s="3">
+        <v>862400</v>
+      </c>
+      <c r="G10" s="3">
         <v>803500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>718400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>823400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>665100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>639700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>604200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>668700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>665100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>602400</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="Q10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R10" s="3">
         <v>628900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>536600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>2127600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>625500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>564200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>624800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>639100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>464300</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>613600</v>
       </c>
-      <c r="Z10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1032,85 +1045,89 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>98300</v>
+      </c>
+      <c r="E12" s="3">
         <v>106600</v>
       </c>
-      <c r="E12" s="3">
-        <v>113000</v>
-      </c>
       <c r="F12" s="3">
+        <v>112700</v>
+      </c>
+      <c r="G12" s="3">
         <v>99800</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>97200</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>115900</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>95300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>113500</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>89000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>93600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>95300</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>113700</v>
       </c>
-      <c r="O12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="Q12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R12" s="3">
         <v>82500</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>73000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>384700</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>83000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>76000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>85400</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>72800</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>77100</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>70400</v>
       </c>
-      <c r="Z12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1186,46 +1203,49 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-35400</v>
+      </c>
+      <c r="E14" s="3">
         <v>84500</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F14" s="3">
+        <v>-22600</v>
+      </c>
+      <c r="G14" s="3">
         <v>-46200</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3">
         <v>268000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>18200</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>11400</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N14" s="3">
         <v>18200</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
@@ -1239,8 +1259,8 @@
       <c r="S14" s="3">
         <v>0</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>3</v>
+      <c r="T14" s="3">
+        <v>0</v>
       </c>
       <c r="U14" s="3" t="s">
         <v>3</v>
@@ -1251,11 +1271,11 @@
       <c r="W14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="3" t="s">
-        <v>3</v>
+      <c r="X14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y14" s="3">
+        <v>0</v>
       </c>
       <c r="Z14" s="3" t="s">
         <v>3</v>
@@ -1263,65 +1283,68 @@
       <c r="AA14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>75400</v>
+      </c>
+      <c r="E15" s="3">
         <v>88600</v>
       </c>
-      <c r="E15" s="3">
-        <v>76000</v>
-      </c>
       <c r="F15" s="3">
+        <v>75500</v>
+      </c>
+      <c r="G15" s="3">
         <v>74500</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>121900</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>120000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>118800</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>71800</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>62800</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>113200</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>118800</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>130200</v>
       </c>
-      <c r="O15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="Q15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R15" s="3">
         <v>39400</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>35700</v>
       </c>
-      <c r="S15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T15" s="3">
+      <c r="T15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U15" s="3">
         <v>35700</v>
       </c>
-      <c r="U15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V15" s="3" t="s">
         <v>3</v>
       </c>
@@ -1340,8 +1363,11 @@
       <c r="AA15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1366,162 +1392,169 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+    </row>
+    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1800500</v>
+      </c>
+      <c r="E17" s="3">
         <v>1918800</v>
       </c>
-      <c r="E17" s="3">
-        <v>1810400</v>
-      </c>
       <c r="F17" s="3">
+        <v>1832500</v>
+      </c>
+      <c r="G17" s="3">
         <v>1606900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1677400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1456900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1568500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1661700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1419200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1433500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1568500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1657300</v>
       </c>
-      <c r="O17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="Q17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R17" s="3">
         <v>1390100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1199200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>4702900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1186000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1028100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1119000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1052000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1282700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1058400</v>
       </c>
-      <c r="Z17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>340500</v>
+      </c>
+      <c r="E18" s="3">
         <v>407900</v>
       </c>
-      <c r="E18" s="3">
-        <v>410500</v>
-      </c>
       <c r="F18" s="3">
+        <v>388500</v>
+      </c>
+      <c r="G18" s="3">
         <v>438200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>270500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>499100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>247500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>168700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>193700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>257300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>247500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>39200</v>
       </c>
-      <c r="O18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="Q18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R18" s="3">
         <v>288800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>175700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>645100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>269900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>225300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>266200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>329500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>153700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>283900</v>
       </c>
-      <c r="Z18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1549,124 +1582,128 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+    </row>
+    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>26300</v>
+      </c>
+      <c r="E20" s="3">
         <v>108400</v>
       </c>
-      <c r="E20" s="3">
-        <v>31900</v>
-      </c>
       <c r="F20" s="3">
+        <v>51500</v>
+      </c>
+      <c r="G20" s="3">
         <v>209100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-3200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>101700</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>5200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>91000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-58400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-7900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>5200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-15700</v>
       </c>
-      <c r="O20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R20" s="3">
         <v>8600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>4300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-11700</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-9400</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>29500</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-51800</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>26600</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-17600</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>38600</v>
       </c>
-      <c r="Z20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>389600</v>
+      </c>
+      <c r="E21" s="3">
         <v>388200</v>
       </c>
-      <c r="E21" s="3">
-        <v>454600</v>
-      </c>
       <c r="F21" s="3">
+        <v>412400</v>
+      </c>
+      <c r="G21" s="3">
         <v>303700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>395600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>517300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>361200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>149500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>314900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>378400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>361200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>185100</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1676,266 +1713,278 @@
       <c r="R21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S21" s="3">
+      <c r="S21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T21" s="3">
         <v>934800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>352000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>301600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>438700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>219800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>403000</v>
       </c>
-      <c r="Z21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>204500</v>
+      </c>
+      <c r="E22" s="3">
         <v>126800</v>
       </c>
-      <c r="E22" s="3">
-        <v>166100</v>
-      </c>
       <c r="F22" s="3">
+        <v>159000</v>
+      </c>
+      <c r="G22" s="3">
         <v>105000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>217000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>100600</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>139200</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>52400</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>108800</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>159800</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>139200</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>146400</v>
       </c>
-      <c r="O22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="Q22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R22" s="3">
         <v>138800</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>90900</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>253500</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>56400</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>55100</v>
       </c>
-      <c r="V22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X22" s="3">
+      <c r="X22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y22" s="3">
         <v>57400</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>61700</v>
       </c>
-      <c r="Z22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>282200</v>
+      </c>
+      <c r="E23" s="3">
         <v>130400</v>
       </c>
-      <c r="E23" s="3">
-        <v>223700</v>
-      </c>
       <c r="F23" s="3">
+        <v>224000</v>
+      </c>
+      <c r="G23" s="3">
         <v>218000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>71800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>97700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>97500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>50100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>152300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>105400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>97500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-91500</v>
       </c>
-      <c r="O23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="Q23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R23" s="3">
         <v>158600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>89100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>379900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>204100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>199700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>214400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>356100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>78700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>260800</v>
       </c>
-      <c r="Z23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>73100</v>
+      </c>
+      <c r="E24" s="3">
         <v>-17200</v>
       </c>
-      <c r="E24" s="3">
-        <v>61200</v>
-      </c>
       <c r="F24" s="3">
+        <v>61300</v>
+      </c>
+      <c r="G24" s="3">
         <v>131000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>45200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>30600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>14600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>12300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>32200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>5900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>14600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-3500</v>
       </c>
-      <c r="O24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="Q24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R24" s="3">
         <v>33500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>22200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>92300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>40800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>39900</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>43600</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>55700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-13300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>49500</v>
       </c>
-      <c r="Z24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2011,162 +2060,171 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>209100</v>
+      </c>
+      <c r="E26" s="3">
         <v>147700</v>
       </c>
-      <c r="E26" s="3">
-        <v>162500</v>
-      </c>
       <c r="F26" s="3">
+        <v>162700</v>
+      </c>
+      <c r="G26" s="3">
         <v>86900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>26500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>67100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>83000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>37800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>120100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>99500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>83000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-87900</v>
       </c>
-      <c r="O26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="Q26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R26" s="3">
         <v>125000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>66900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>287600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>163300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>159700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>170800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>300400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>92000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>211300</v>
       </c>
-      <c r="Z26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>175900</v>
+      </c>
+      <c r="E27" s="3">
         <v>115400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
+        <v>137700</v>
+      </c>
+      <c r="G27" s="3">
+        <v>71500</v>
+      </c>
+      <c r="H27" s="3">
+        <v>15900</v>
+      </c>
+      <c r="I27" s="3">
+        <v>43100</v>
+      </c>
+      <c r="J27" s="3">
+        <v>41700</v>
+      </c>
+      <c r="K27" s="3">
+        <v>21400</v>
+      </c>
+      <c r="L27" s="3">
+        <v>94400</v>
+      </c>
+      <c r="M27" s="3">
+        <v>63000</v>
+      </c>
+      <c r="N27" s="3">
+        <v>41700</v>
+      </c>
+      <c r="O27" s="3">
+        <v>-117600</v>
+      </c>
+      <c r="P27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R27" s="3">
+        <v>98300</v>
+      </c>
+      <c r="S27" s="3">
+        <v>57800</v>
+      </c>
+      <c r="T27" s="3">
+        <v>204600</v>
+      </c>
+      <c r="U27" s="3">
+        <v>147400</v>
+      </c>
+      <c r="V27" s="3">
         <v>137500</v>
       </c>
-      <c r="F27" s="3">
-        <v>71500</v>
-      </c>
-      <c r="G27" s="3">
-        <v>15900</v>
-      </c>
-      <c r="H27" s="3">
-        <v>43100</v>
-      </c>
-      <c r="I27" s="3">
-        <v>41700</v>
-      </c>
-      <c r="J27" s="3">
-        <v>21400</v>
-      </c>
-      <c r="K27" s="3">
-        <v>94400</v>
-      </c>
-      <c r="L27" s="3">
-        <v>63000</v>
-      </c>
-      <c r="M27" s="3">
-        <v>41700</v>
-      </c>
-      <c r="N27" s="3">
-        <v>-117600</v>
-      </c>
-      <c r="O27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q27" s="3">
-        <v>98300</v>
-      </c>
-      <c r="R27" s="3">
-        <v>57800</v>
-      </c>
-      <c r="S27" s="3">
-        <v>204600</v>
-      </c>
-      <c r="T27" s="3">
-        <v>147400</v>
-      </c>
-      <c r="U27" s="3">
-        <v>137500</v>
-      </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>140600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>281600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>64700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>193400</v>
       </c>
-      <c r="Z27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2242,8 +2300,11 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2286,8 +2347,8 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-      <c r="Q29" s="3" t="s">
-        <v>3</v>
+      <c r="Q29" s="3">
+        <v>0</v>
       </c>
       <c r="R29" s="3" t="s">
         <v>3</v>
@@ -2295,8 +2356,8 @@
       <c r="S29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T29" s="3">
-        <v>0</v>
+      <c r="T29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U29" s="3">
         <v>0</v>
@@ -2305,22 +2366,25 @@
         <v>0</v>
       </c>
       <c r="W29" s="3">
+        <v>0</v>
+      </c>
+      <c r="X29" s="3">
         <v>-8600</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>-31700</v>
       </c>
-      <c r="Y29" s="3">
-        <v>0</v>
-      </c>
       <c r="Z29" s="3">
         <v>0</v>
       </c>
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2396,8 +2460,11 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2473,162 +2540,171 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-26300</v>
+      </c>
+      <c r="E32" s="3">
         <v>-108400</v>
       </c>
-      <c r="E32" s="3">
-        <v>-31900</v>
-      </c>
       <c r="F32" s="3">
+        <v>-51500</v>
+      </c>
+      <c r="G32" s="3">
         <v>-209100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>3200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-101700</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-5200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-91000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>58400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>7900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-5200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>15700</v>
       </c>
-      <c r="O32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R32" s="3">
         <v>-8600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-4300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>11700</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>9400</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-29500</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>51800</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-26600</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>17600</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-38600</v>
       </c>
-      <c r="Z32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>175900</v>
+      </c>
+      <c r="E33" s="3">
         <v>115400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
+        <v>137700</v>
+      </c>
+      <c r="G33" s="3">
+        <v>71500</v>
+      </c>
+      <c r="H33" s="3">
+        <v>15900</v>
+      </c>
+      <c r="I33" s="3">
+        <v>43100</v>
+      </c>
+      <c r="J33" s="3">
+        <v>41700</v>
+      </c>
+      <c r="K33" s="3">
+        <v>21400</v>
+      </c>
+      <c r="L33" s="3">
+        <v>94400</v>
+      </c>
+      <c r="M33" s="3">
+        <v>63000</v>
+      </c>
+      <c r="N33" s="3">
+        <v>41700</v>
+      </c>
+      <c r="O33" s="3">
+        <v>-117600</v>
+      </c>
+      <c r="P33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R33" s="3">
+        <v>98300</v>
+      </c>
+      <c r="S33" s="3">
+        <v>57800</v>
+      </c>
+      <c r="T33" s="3">
+        <v>204600</v>
+      </c>
+      <c r="U33" s="3">
+        <v>147400</v>
+      </c>
+      <c r="V33" s="3">
         <v>137500</v>
       </c>
-      <c r="F33" s="3">
-        <v>71500</v>
-      </c>
-      <c r="G33" s="3">
-        <v>15900</v>
-      </c>
-      <c r="H33" s="3">
-        <v>43100</v>
-      </c>
-      <c r="I33" s="3">
-        <v>41700</v>
-      </c>
-      <c r="J33" s="3">
-        <v>21400</v>
-      </c>
-      <c r="K33" s="3">
-        <v>94400</v>
-      </c>
-      <c r="L33" s="3">
-        <v>63000</v>
-      </c>
-      <c r="M33" s="3">
-        <v>41700</v>
-      </c>
-      <c r="N33" s="3">
-        <v>-117600</v>
-      </c>
-      <c r="O33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q33" s="3">
-        <v>98300</v>
-      </c>
-      <c r="R33" s="3">
-        <v>57800</v>
-      </c>
-      <c r="S33" s="3">
-        <v>204600</v>
-      </c>
-      <c r="T33" s="3">
-        <v>147400</v>
-      </c>
-      <c r="U33" s="3">
-        <v>137500</v>
-      </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>140600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>273000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>33100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>193400</v>
       </c>
-      <c r="Z33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2704,167 +2780,176 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>175900</v>
+      </c>
+      <c r="E35" s="3">
         <v>115400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
+        <v>137700</v>
+      </c>
+      <c r="G35" s="3">
+        <v>71500</v>
+      </c>
+      <c r="H35" s="3">
+        <v>15900</v>
+      </c>
+      <c r="I35" s="3">
+        <v>43100</v>
+      </c>
+      <c r="J35" s="3">
+        <v>41700</v>
+      </c>
+      <c r="K35" s="3">
+        <v>21400</v>
+      </c>
+      <c r="L35" s="3">
+        <v>94400</v>
+      </c>
+      <c r="M35" s="3">
+        <v>63000</v>
+      </c>
+      <c r="N35" s="3">
+        <v>41700</v>
+      </c>
+      <c r="O35" s="3">
+        <v>-117600</v>
+      </c>
+      <c r="P35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R35" s="3">
+        <v>98300</v>
+      </c>
+      <c r="S35" s="3">
+        <v>57800</v>
+      </c>
+      <c r="T35" s="3">
+        <v>204600</v>
+      </c>
+      <c r="U35" s="3">
+        <v>147400</v>
+      </c>
+      <c r="V35" s="3">
         <v>137500</v>
       </c>
-      <c r="F35" s="3">
-        <v>71500</v>
-      </c>
-      <c r="G35" s="3">
-        <v>15900</v>
-      </c>
-      <c r="H35" s="3">
-        <v>43100</v>
-      </c>
-      <c r="I35" s="3">
-        <v>41700</v>
-      </c>
-      <c r="J35" s="3">
-        <v>21400</v>
-      </c>
-      <c r="K35" s="3">
-        <v>94400</v>
-      </c>
-      <c r="L35" s="3">
-        <v>63000</v>
-      </c>
-      <c r="M35" s="3">
-        <v>41700</v>
-      </c>
-      <c r="N35" s="3">
-        <v>-117600</v>
-      </c>
-      <c r="O35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q35" s="3">
-        <v>98300</v>
-      </c>
-      <c r="R35" s="3">
-        <v>57800</v>
-      </c>
-      <c r="S35" s="3">
-        <v>204600</v>
-      </c>
-      <c r="T35" s="3">
-        <v>147400</v>
-      </c>
-      <c r="U35" s="3">
-        <v>137500</v>
-      </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>140600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>273000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>33100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>193400</v>
       </c>
-      <c r="Z35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45657</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44377</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44286</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44196</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44104</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44012</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43921</v>
       </c>
-      <c r="Z38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AA38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2892,8 +2977,9 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2921,701 +3007,729 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+    </row>
+    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>586100</v>
+      </c>
+      <c r="E41" s="3">
         <v>968700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>656100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1014600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2264200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>585400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>571300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>585600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>548900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>512500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>571300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>462500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>606900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>567500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>713200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>431700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>413000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>624200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1093100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>929400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>896700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>911700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>47700</v>
       </c>
-      <c r="Z41" s="3">
-        <v>0</v>
-      </c>
       <c r="AA41" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>27400</v>
+      </c>
+      <c r="E42" s="3">
         <v>28200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>27800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>24800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>156800</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>128700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>19400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>33100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>25100</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
       <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3">
         <v>19400</v>
       </c>
-      <c r="N42" s="3">
-        <v>0</v>
-      </c>
       <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3">
         <v>48400</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>39400</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>2208500</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>10500</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>6600</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>12000</v>
-      </c>
-      <c r="U42" s="3">
-        <v>13000</v>
       </c>
       <c r="V42" s="3">
         <v>13000</v>
       </c>
       <c r="W42" s="3">
+        <v>13000</v>
+      </c>
+      <c r="X42" s="3">
         <v>12600</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>12800</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>13500</v>
       </c>
-      <c r="Z42" s="3">
-        <v>0</v>
-      </c>
       <c r="AA42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1358400</v>
+      </c>
+      <c r="E43" s="3">
         <v>1006200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1470800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1118100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1001900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>896400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>945100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>806700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>808000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>961100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>945100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>960700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>857100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>835300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>545800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>699500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>537500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>560200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>601300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>566000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>546100</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>555200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>526900</v>
       </c>
-      <c r="Z43" s="3">
-        <v>0</v>
-      </c>
       <c r="AA43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>3989500</v>
+      </c>
+      <c r="E44" s="3">
         <v>3869900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>3930600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>3685700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>3882200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>3849200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>3621700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>3421300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>3066700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>3690400</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>3621700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>3560500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>3545800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>3170400</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>2458400</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>2305000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>2317800</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>2156300</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>2101300</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>2206000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>2128500</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>2164100</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>2552700</v>
       </c>
-      <c r="Z44" s="3">
-        <v>0</v>
-      </c>
       <c r="AA44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>99400</v>
+      </c>
+      <c r="E45" s="3">
         <v>84500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>75800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>87000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>103900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1317100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>87900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>126600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>185100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>144400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>87900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>132500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>96100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>177900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>69700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>68200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>70200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>55700</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>46300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>45900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>44300</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>45000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>661900</v>
       </c>
-      <c r="Z45" s="3">
-        <v>0</v>
-      </c>
       <c r="AA45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>6060800</v>
+      </c>
+      <c r="E46" s="3">
         <v>5957500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>6161100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>5930200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>7409100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>6776800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>5245400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>4973400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>4633900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>5308400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>5245400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>5116100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>5154300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>4790500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>5995700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>3514900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>3345100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>3408300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>3854900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>3760300</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>3628100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>3688900</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>3802600</v>
       </c>
-      <c r="Z46" s="3">
-        <v>0</v>
-      </c>
       <c r="AA46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>459300</v>
+      </c>
+      <c r="E47" s="3">
         <v>540100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>553200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>547700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>600000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>499500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>2621700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>2611000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>2559700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>2749000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>2621700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>2799800</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>2853100</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>2798000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>2570100</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>2318600</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>2308900</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>2226100</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>2157600</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>2191200</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>2114100</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>2149600</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>2169000</v>
       </c>
-      <c r="Z47" s="3">
-        <v>0</v>
-      </c>
       <c r="AA47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4633800</v>
+      </c>
+      <c r="E48" s="3">
         <v>4757500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>4740300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>4462200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>4515800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>4634000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>4468800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>4454900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>4419700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>3470200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>4468800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>3498900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>4617000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>4569100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>3637700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>3401600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>2626900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>3233700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>2300100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>3080400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>2972100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>3021800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>2293700</v>
       </c>
-      <c r="Z48" s="3">
-        <v>0</v>
-      </c>
       <c r="AA48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>11220200</v>
+      </c>
+      <c r="E49" s="3">
         <v>9205100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>11272700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>8896400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>10696400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>8853400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>10675800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>8911400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>10019700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>11511700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>10675800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>11567600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>11032900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>10358300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>8558800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>8201900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>9060000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>7419800</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>8108100</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>7338000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>7080000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>7198600</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>8097000</v>
       </c>
-      <c r="Z49" s="3">
-        <v>0</v>
-      </c>
       <c r="AA49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3691,8 +3805,11 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3768,85 +3885,91 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>20600</v>
+      </c>
+      <c r="E52" s="3">
         <v>18800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>12300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>152200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>153600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>160900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>23100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>38800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>45300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>314300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>23100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>214900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>193700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>221000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>165900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>154200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>153900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>161400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>133700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>132300</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>127600</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>129800</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>136500</v>
       </c>
-      <c r="Z52" s="3">
-        <v>0</v>
-      </c>
       <c r="AA52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3922,85 +4045,91 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>22952100</v>
+      </c>
+      <c r="E54" s="3">
         <v>23144300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>23214500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>22160700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>23884600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>23203400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>23398200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>23013800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>21993600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>23353600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>23398200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>23197300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>23851000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>22736900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>20928300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>17591200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>17494800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>16449400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>16554400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>16502200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>15921900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>16188700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>16498900</v>
       </c>
-      <c r="Z54" s="3">
-        <v>0</v>
-      </c>
       <c r="AA54" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB54" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4028,8 +4157,9 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+    </row>
+    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4057,470 +4187,489 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+    </row>
+    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1143600</v>
+      </c>
+      <c r="E57" s="3">
         <v>987400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1031900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>882100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>940500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>909600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>774000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>782200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>733000</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M57" s="3">
+      <c r="M57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N57" s="3">
         <v>774000</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O57" s="3">
+      <c r="O57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P57" s="3">
         <v>810700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>757700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>684400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>629600</v>
       </c>
-      <c r="S57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T57" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V57" s="3">
+      <c r="V57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W57" s="3">
         <v>583900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>563400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>572800</v>
       </c>
-      <c r="Y57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z57" s="3">
-        <v>0</v>
+      <c r="Z57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>626100</v>
+      </c>
+      <c r="E58" s="3">
         <v>648100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>613200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>699900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2954400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1131400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>799300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>849600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>420700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>801500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>799300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>827200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>754600</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>433700</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>2703000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1037100</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>690700</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>457300</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>338500</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>332500</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>320800</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>326100</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>344000</v>
       </c>
-      <c r="Z58" s="3">
-        <v>0</v>
-      </c>
       <c r="AA58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>784900</v>
+      </c>
+      <c r="E59" s="3">
         <v>169100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>692200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>184300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>511000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>120000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>475800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>122500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>577800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1341900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>475800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1390700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>601000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>598600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>393000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>418100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1001400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>980500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>978200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>396200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>382300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>388700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1040400</v>
       </c>
-      <c r="Z59" s="3">
-        <v>0</v>
-      </c>
       <c r="AA59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2554600</v>
+      </c>
+      <c r="E60" s="3">
         <v>2370600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2337200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2232100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>4405800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2570400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2049100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2090300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1731500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2143400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2049100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2217800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2166300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1790000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>3780400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>2084800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1692100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1437800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1316700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1312600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1266400</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1287600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1384400</v>
       </c>
-      <c r="Z60" s="3">
-        <v>0</v>
-      </c>
       <c r="AA60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>10062800</v>
+      </c>
+      <c r="E61" s="3">
         <v>10673900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>10707700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>9826100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>9377800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>11090500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>11132200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>10639900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>10562100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>10901200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>11132200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>10863300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>10044700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>9893800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>7812000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>7571100</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>7297000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>7109800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>7118400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>6820900</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>6581100</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>6691300</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>7123800</v>
       </c>
-      <c r="Z61" s="3">
-        <v>0</v>
-      </c>
       <c r="AA61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>141700</v>
+      </c>
+      <c r="E62" s="3">
         <v>27000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>144400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>24800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>136200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>18500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>128500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>22300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>149700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1239700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>128500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1234000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2272500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1954300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1374200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>408500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>703600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>665000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>599100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>919500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>887200</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>902100</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>511000</v>
       </c>
-      <c r="Z62" s="3">
-        <v>0</v>
-      </c>
       <c r="AA62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4596,8 +4745,11 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4673,8 +4825,11 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4750,85 +4905,91 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>13835300</v>
+      </c>
+      <c r="E66" s="3">
         <v>14217400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>14291300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>13250900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>14996400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>14898200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>14420500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>13975000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>13192200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>14284300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>14420500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>14315100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>17061500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>15896300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>14918100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>11983700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>11615600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>10948200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>10897200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>10826100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>10445400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>10620400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>10745200</v>
       </c>
-      <c r="Z66" s="3">
-        <v>0</v>
-      </c>
       <c r="AA66" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB66" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4856,8 +5017,9 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+    </row>
+    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4933,8 +5095,11 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5010,8 +5175,11 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5087,8 +5255,11 @@
       <c r="AA70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5164,85 +5335,91 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>323300</v>
+      </c>
+      <c r="E72" s="3">
         <v>422700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>266600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>213300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>79400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>87700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-20200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>275000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>200000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>3500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-20200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-117600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>5022700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>4824500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>4702900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>4779400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>4905800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>4733500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>4632400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>4352300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>4199300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>4269600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>4230100</v>
       </c>
-      <c r="Z72" s="3">
-        <v>0</v>
-      </c>
       <c r="AA72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5318,8 +5495,11 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5395,8 +5575,11 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5472,85 +5655,91 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>6336100</v>
+      </c>
+      <c r="E76" s="3">
         <v>6188800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>6070600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>6090700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>5992400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>5933900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>6399400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>6551200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>6617000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>6485100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>6399400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>6359000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>6789500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>6840700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>6010200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>5607500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>5879200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>5501200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>5657200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>5676100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>5476500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>5568300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>5753600</v>
       </c>
-      <c r="Z76" s="3">
-        <v>0</v>
-      </c>
       <c r="AA76" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB76" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5626,167 +5815,176 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45657</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44377</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44286</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44196</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44104</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44012</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43921</v>
       </c>
-      <c r="Z80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AA80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>175900</v>
+      </c>
+      <c r="E81" s="3">
         <v>115400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
+        <v>137700</v>
+      </c>
+      <c r="G81" s="3">
+        <v>71500</v>
+      </c>
+      <c r="H81" s="3">
+        <v>15900</v>
+      </c>
+      <c r="I81" s="3">
+        <v>43100</v>
+      </c>
+      <c r="J81" s="3">
+        <v>41700</v>
+      </c>
+      <c r="K81" s="3">
+        <v>21400</v>
+      </c>
+      <c r="L81" s="3">
+        <v>94400</v>
+      </c>
+      <c r="M81" s="3">
+        <v>63000</v>
+      </c>
+      <c r="N81" s="3">
+        <v>41700</v>
+      </c>
+      <c r="O81" s="3">
+        <v>-117600</v>
+      </c>
+      <c r="P81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R81" s="3">
+        <v>98300</v>
+      </c>
+      <c r="S81" s="3">
+        <v>57800</v>
+      </c>
+      <c r="T81" s="3">
+        <v>204600</v>
+      </c>
+      <c r="U81" s="3">
+        <v>147400</v>
+      </c>
+      <c r="V81" s="3">
         <v>137500</v>
       </c>
-      <c r="F81" s="3">
-        <v>71500</v>
-      </c>
-      <c r="G81" s="3">
-        <v>15900</v>
-      </c>
-      <c r="H81" s="3">
-        <v>43100</v>
-      </c>
-      <c r="I81" s="3">
-        <v>41700</v>
-      </c>
-      <c r="J81" s="3">
-        <v>21400</v>
-      </c>
-      <c r="K81" s="3">
-        <v>94400</v>
-      </c>
-      <c r="L81" s="3">
-        <v>63000</v>
-      </c>
-      <c r="M81" s="3">
-        <v>41700</v>
-      </c>
-      <c r="N81" s="3">
-        <v>-117600</v>
-      </c>
-      <c r="O81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q81" s="3">
-        <v>98300</v>
-      </c>
-      <c r="R81" s="3">
-        <v>57800</v>
-      </c>
-      <c r="S81" s="3">
-        <v>204600</v>
-      </c>
-      <c r="T81" s="3">
-        <v>147400</v>
-      </c>
-      <c r="U81" s="3">
-        <v>137500</v>
-      </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>140600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>273000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>33100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>193400</v>
       </c>
-      <c r="Z81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5814,47 +6012,48 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+    </row>
+    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>121900</v>
+      </c>
+      <c r="E83" s="3">
         <v>50800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>118800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>62300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>103300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>41400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>42200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>100800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>28100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>101800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>103300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>98200</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P83" s="3" t="s">
         <v>3</v>
       </c>
@@ -5864,35 +6063,38 @@
       <c r="R83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S83" s="3">
+      <c r="S83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T83" s="3">
         <v>301400</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>91500</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>-253700</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>87200</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>82600</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>83700</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>80500</v>
       </c>
-      <c r="Z83" s="3">
-        <v>0</v>
-      </c>
       <c r="AA83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5968,8 +6170,11 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6045,8 +6250,11 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6122,8 +6330,11 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6199,8 +6410,11 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6276,47 +6490,50 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>259300</v>
+      </c>
+      <c r="E89" s="3">
         <v>505900</v>
       </c>
-      <c r="E89" s="3">
-        <v>182300</v>
-      </c>
       <c r="F89" s="3">
+        <v>185000</v>
+      </c>
+      <c r="G89" s="3">
         <v>532600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>270900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>184400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-20600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>72100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-3600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>164700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-20600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-66800</v>
       </c>
-      <c r="O89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P89" s="3" t="s">
         <v>3</v>
       </c>
@@ -6326,35 +6543,38 @@
       <c r="R89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S89" s="3">
+      <c r="S89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T89" s="3">
         <v>454600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>174100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-986800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>273700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>317400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>451800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>109400</v>
       </c>
-      <c r="Z89" s="3">
-        <v>0</v>
-      </c>
       <c r="AA89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6382,85 +6602,89 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+    </row>
+    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-75400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-100500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
+        <v>-70300</v>
+      </c>
+      <c r="G91" s="3">
+        <v>-104100</v>
+      </c>
+      <c r="H91" s="3">
+        <v>-32700</v>
+      </c>
+      <c r="I91" s="3">
+        <v>-103600</v>
+      </c>
+      <c r="J91" s="3">
+        <v>-51500</v>
+      </c>
+      <c r="K91" s="3">
+        <v>-66800</v>
+      </c>
+      <c r="L91" s="3">
+        <v>-63300</v>
+      </c>
+      <c r="M91" s="3">
+        <v>-47900</v>
+      </c>
+      <c r="N91" s="3">
+        <v>-51500</v>
+      </c>
+      <c r="O91" s="3">
+        <v>-46400</v>
+      </c>
+      <c r="P91" s="3">
+        <v>-232500</v>
+      </c>
+      <c r="Q91" s="3">
+        <v>-143000</v>
+      </c>
+      <c r="R91" s="3">
+        <v>-182500</v>
+      </c>
+      <c r="S91" s="3">
+        <v>-72800</v>
+      </c>
+      <c r="T91" s="3">
+        <v>-59800</v>
+      </c>
+      <c r="U91" s="3">
+        <v>-102500</v>
+      </c>
+      <c r="V91" s="3">
+        <v>241900</v>
+      </c>
+      <c r="W91" s="3">
         <v>-70800</v>
       </c>
-      <c r="F91" s="3">
-        <v>-104100</v>
-      </c>
-      <c r="G91" s="3">
-        <v>-32700</v>
-      </c>
-      <c r="H91" s="3">
-        <v>-103600</v>
-      </c>
-      <c r="I91" s="3">
-        <v>-51500</v>
-      </c>
-      <c r="J91" s="3">
-        <v>-66800</v>
-      </c>
-      <c r="K91" s="3">
-        <v>-63300</v>
-      </c>
-      <c r="L91" s="3">
-        <v>-47900</v>
-      </c>
-      <c r="M91" s="3">
-        <v>-51500</v>
-      </c>
-      <c r="N91" s="3">
-        <v>-46400</v>
-      </c>
-      <c r="O91" s="3">
-        <v>-232500</v>
-      </c>
-      <c r="P91" s="3">
-        <v>-143000</v>
-      </c>
-      <c r="Q91" s="3">
-        <v>-182500</v>
-      </c>
-      <c r="R91" s="3">
-        <v>-72800</v>
-      </c>
-      <c r="S91" s="3">
-        <v>-59800</v>
-      </c>
-      <c r="T91" s="3">
-        <v>-102500</v>
-      </c>
-      <c r="U91" s="3">
-        <v>241900</v>
-      </c>
-      <c r="V91" s="3">
-        <v>-70800</v>
-      </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-78900</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-78600</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-62500</v>
       </c>
-      <c r="Z91" s="3">
-        <v>0</v>
-      </c>
       <c r="AA91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6536,8 +6760,11 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6613,47 +6840,50 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-146200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-177700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-126400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-185300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>1445800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-153600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-56500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-153900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1689100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-130100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-56500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-90200</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P94" s="3" t="s">
         <v>3</v>
       </c>
@@ -6663,35 +6893,38 @@
       <c r="R94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S94" s="3">
+      <c r="S94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T94" s="3">
         <v>-311300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-60700</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>308000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-584000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-84800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-113900</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-117600</v>
       </c>
-      <c r="Z94" s="3">
-        <v>0</v>
-      </c>
       <c r="AA94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6719,8 +6952,9 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+    </row>
+    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6757,8 +6991,8 @@
       <c r="N96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -6796,8 +7030,11 @@
       <c r="AA96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6873,8 +7110,11 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6950,8 +7190,11 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7027,47 +7270,50 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-337000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-88300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-213000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-28400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>63700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>35300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>201900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>216100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-460900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-84000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>201900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>31500</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P100" s="3" t="s">
         <v>3</v>
       </c>
@@ -7077,74 +7323,77 @@
       <c r="R100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S100" s="3">
+      <c r="S100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T100" s="3">
         <v>2307900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-90200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>553600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-140900</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-43700</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-71000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-114200</v>
       </c>
-      <c r="Z100" s="3">
-        <v>0</v>
-      </c>
       <c r="AA100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E101" s="3">
         <v>-17300</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-61200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>39700</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>21800</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>22200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-5500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-33100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>44300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>39700</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>16400</v>
       </c>
-      <c r="O101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P101" s="3" t="s">
         <v>3</v>
       </c>
@@ -7154,74 +7403,77 @@
       <c r="R101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S101" s="3">
+      <c r="S101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T101" s="3">
         <v>36500</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-5000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>86700</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-28600</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-30900</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-17100</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>14200</v>
       </c>
-      <c r="Z101" s="3">
-        <v>0</v>
-      </c>
       <c r="AA101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-215900</v>
+      </c>
+      <c r="E102" s="3">
         <v>239300</v>
       </c>
-      <c r="E102" s="3">
-        <v>-228000</v>
-      </c>
       <c r="F102" s="3">
+        <v>-225500</v>
+      </c>
+      <c r="G102" s="3">
         <v>347500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1783600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>48800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>124600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>73100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-2113900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-41400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>124600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-132900</v>
       </c>
-      <c r="O102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P102" s="3" t="s">
         <v>3</v>
       </c>
@@ -7231,31 +7483,34 @@
       <c r="R102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S102" s="3">
+      <c r="S102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T102" s="3">
         <v>2487600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>18200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-38400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-479900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>158000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>249800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-108200</v>
       </c>
-      <c r="Z102" s="3">
-        <v>0</v>
-      </c>
       <c r="AA102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB102" s="3">
         <v>0</v>
       </c>
     </row>
